--- a/artfynd/A 36373-2023 artfynd.xlsx
+++ b/artfynd/A 36373-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36373-2023 artfynd.xlsx
+++ b/artfynd/A 36373-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89603571</v>
+        <v>89603563</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448727.1051419313</v>
+        <v>449114</v>
       </c>
       <c r="R2" t="n">
-        <v>7087542.843225029</v>
+        <v>7087319</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89603578</v>
+        <v>89603568</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449364.1703462857</v>
+        <v>448743</v>
       </c>
       <c r="R3" t="n">
-        <v>7087190.798502544</v>
+        <v>7087495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89603568</v>
+        <v>89603578</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448743.0745225498</v>
+        <v>449364</v>
       </c>
       <c r="R4" t="n">
-        <v>7087495.031241547</v>
+        <v>7087191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89603584</v>
+        <v>89603579</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449194.1072894864</v>
+        <v>448735</v>
       </c>
       <c r="R5" t="n">
-        <v>7087116.936636317</v>
+        <v>7087524</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,16 +1082,11 @@
         <v>89603575</v>
       </c>
       <c r="B6" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1164,12 +1099,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448734.8806914946</v>
+        <v>448735</v>
       </c>
       <c r="R6" t="n">
-        <v>7087506.172544261</v>
+        <v>7087506</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89603572</v>
+        <v>111936858</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,34 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartrun, Jmt</t>
+          <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448735.1762845191</v>
+        <v>448738</v>
       </c>
       <c r="R7" t="n">
-        <v>7087524.219270944</v>
+        <v>7087497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,22 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,31 +1265,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>89603553</v>
       </c>
       <c r="B8" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449171.1812618052</v>
+        <v>449171</v>
       </c>
       <c r="R8" t="n">
-        <v>7087144.169174721</v>
+        <v>7087144</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1345,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,50 +1378,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89603579</v>
+        <v>111936792</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartrun, Jmt</t>
+          <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448735.1762845191</v>
+        <v>448761</v>
       </c>
       <c r="R9" t="n">
-        <v>7087524.219270944</v>
+        <v>7087579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,22 +1443,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,70 +1463,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111936798</v>
+        <v>89603572</v>
       </c>
       <c r="B10" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>rörvattsbodarna, Jmt</t>
+          <t>Svartrun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448923</v>
+        <v>448735</v>
       </c>
       <c r="R10" t="n">
-        <v>7087371</v>
+        <v>7087524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,17 +1540,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,62 +1560,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111936865</v>
+        <v>89603584</v>
       </c>
       <c r="B11" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>rörvattsbodarna, Jmt</t>
+          <t>Svartrun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448738</v>
+        <v>449194</v>
       </c>
       <c r="R11" t="n">
-        <v>7087426</v>
+        <v>7087117</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,12 +1641,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,27 +1661,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111936858</v>
+        <v>111936893</v>
       </c>
       <c r="B12" t="n">
-        <v>89993</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,21 +1688,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448737</v>
+        <v>448742</v>
       </c>
       <c r="R12" t="n">
-        <v>7087496</v>
+        <v>7087501</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,15 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111936795</v>
+        <v>89603571</v>
       </c>
       <c r="B13" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,38 +1785,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>rörvattsbodarna, Jmt</t>
+          <t>Svartrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448749</v>
+        <v>448727</v>
       </c>
       <c r="R13" t="n">
-        <v>7087422</v>
+        <v>7087543</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,17 +1839,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,66 +1859,61 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111936796</v>
+        <v>89603560</v>
       </c>
       <c r="B14" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>rörvattsbodarna, Jmt</t>
+          <t>Svartrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448883</v>
+        <v>449017</v>
       </c>
       <c r="R14" t="n">
-        <v>7087229</v>
+        <v>7087329</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,17 +1940,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,27 +1960,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111936870</v>
+        <v>111936795</v>
       </c>
       <c r="B15" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,34 +1987,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449019</v>
+        <v>448749</v>
       </c>
       <c r="R15" t="n">
-        <v>7087277</v>
+        <v>7087422</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,6 +2051,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,50 +2082,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111936792</v>
+        <v>111936796</v>
       </c>
       <c r="B16" t="n">
-        <v>90235</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448761</v>
+        <v>448883</v>
       </c>
       <c r="R16" t="n">
-        <v>7087579</v>
+        <v>7087230</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2318,6 +2157,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,15 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111936893</v>
+        <v>111936798</v>
       </c>
       <c r="B17" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,34 +2199,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448742</v>
+        <v>448923</v>
       </c>
       <c r="R17" t="n">
-        <v>7087502</v>
+        <v>7087371</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2420,6 +2263,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2446,15 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111936869</v>
+        <v>111936799</v>
       </c>
       <c r="B18" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,34 +2305,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449144</v>
+        <v>448826</v>
       </c>
       <c r="R18" t="n">
-        <v>7087118</v>
+        <v>7087529</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,6 +2369,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,50 +2400,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111936866</v>
+        <v>89603565</v>
       </c>
       <c r="B19" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80398</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>229748</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>rörvattsbodarna, Jmt</t>
+          <t>Svartrun, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448766</v>
+        <v>449017</v>
       </c>
       <c r="R19" t="n">
-        <v>7087417</v>
+        <v>7087329</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,12 +2465,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2638,219 +2485,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>111936867</v>
-      </c>
-      <c r="B20" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>448792</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7087386</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>111936868</v>
-      </c>
-      <c r="B21" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>448988</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7087187</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36373-2023 artfynd.xlsx
+++ b/artfynd/A 36373-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603568</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603579</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603575</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936858</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936792</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603572</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936893</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603571</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1567,6 +1612,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603560</t>
         </is>
       </c>
     </row>
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936795</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1781,6 +1836,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936796</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1887,6 +1947,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936798</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936799</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2094,6 +2164,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603565</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2195,6 +2270,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603563</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2296,6 +2376,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603578</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2397,6 +2482,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603553</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2498,8 +2588,33 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603584</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>